--- a/Excel/pspl_dpy.xlsx
+++ b/Excel/pspl_dpy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel-Files\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A2BA631-0718-4413-A7CE-DF5B1802B9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818EDE49-375B-45E9-8DD3-C3BA9BAE2672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{3F9CAC95-6A7B-465F-8F4E-259BE180575F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>DPY  REPORT</t>
   </si>
@@ -50,6 +50,21 @@
   </si>
   <si>
     <t>ADDRESS  -   Vill-Ghotia, Kh No. 208/1, 208/2, 208/3, 208/4, 202, Tehsil- Khairagarh,  District- Khairagarh/ Chhuikhadan/ Gandai (C.G.)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">M/s Pilania Steels Pvt. Ltd. Unit II </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="4" tint="-0.249977111117893"/>
+        <rFont val="Book Antiqua"/>
+        <family val="1"/>
+      </rPr>
+      <t>(DC : 1.8 MWp)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -138,19 +153,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -469,10 +484,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC73F8FB-3742-48B6-957B-C5DAA5835575}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -512,44 +530,44 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -574,55 +592,55 @@
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
